--- a/diseases/d093/2026-2029.xlsx
+++ b/diseases/d093/2026-2029.xlsx
@@ -869,12 +869,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -913,15 +913,12 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -950,42 +947,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1014,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1047,7 +1044,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1056,20 +1053,17 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1098,42 +1092,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1159,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1195,7 +1189,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1204,20 +1198,17 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1246,42 +1237,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1304,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1343,7 +1334,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1357,15 +1348,12 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1394,42 +1382,42 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1449,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1491,7 +1479,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1505,15 +1493,12 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1542,42 +1527,42 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1594,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1639,12 +1624,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1653,15 +1638,12 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1695,12 +1677,12 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1715,12 +1697,12 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -1757,12 +1739,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1787,12 +1769,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1801,15 +1783,12 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1838,42 +1817,42 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1884,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1935,12 +1914,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1949,15 +1928,12 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1986,42 +1962,42 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2059,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2231,25 +2207,25 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2349,12 +2325,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2379,25 +2355,25 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2430,42 +2406,42 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -2527,25 +2503,25 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2675,12 +2651,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2793,12 +2769,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2823,25 +2799,25 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2874,42 +2850,42 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -2941,12 +2917,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2971,12 +2947,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -2985,15 +2961,12 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3022,42 +2995,42 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3062,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3119,12 +3092,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3138,7 +3111,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3172,12 +3145,12 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3192,12 +3165,12 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -3234,12 +3207,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3264,12 +3237,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3278,15 +3251,12 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3315,42 +3285,42 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3352,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3412,12 +3382,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3426,15 +3396,12 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3463,42 +3430,42 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3530,12 +3497,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3560,12 +3527,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3574,15 +3541,12 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3611,42 +3575,42 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3678,12 +3642,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3708,12 +3672,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3722,15 +3686,12 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3759,42 +3720,42 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3826,12 +3787,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3856,12 +3817,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -3875,7 +3836,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3909,12 +3870,12 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3929,12 +3890,12 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -3971,12 +3932,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4001,12 +3962,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4015,15 +3976,12 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4052,42 +4010,42 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4107,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4297,25 +4255,25 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -4445,12 +4403,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4593,12 +4551,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4741,18 +4699,21 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
@@ -4886,12 +4847,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4900,9 +4861,12 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5028,12 +4992,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5042,9 +5006,12 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5170,12 +5137,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5184,9 +5151,12 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5312,12 +5282,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5326,9 +5296,12 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5454,12 +5427,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5468,9 +5441,12 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5596,12 +5572,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5610,9 +5586,12 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5738,12 +5717,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5752,9 +5731,12 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5880,12 +5862,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -5894,9 +5876,12 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6022,22 +6007,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6167,18 +6155,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
@@ -6312,22 +6303,25 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -6457,18 +6451,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
@@ -6602,12 +6599,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6747,12 +6744,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6761,9 +6758,12 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -6903,9 +6903,12 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7031,12 +7034,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7045,9 +7048,12 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7173,12 +7179,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7187,9 +7193,12 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7315,12 +7324,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7329,9 +7338,12 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7457,12 +7469,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7471,9 +7483,12 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7599,12 +7614,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7613,9 +7628,12 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7741,12 +7759,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7755,9 +7773,12 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7883,18 +7904,21 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
@@ -8028,18 +8052,21 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
@@ -8173,18 +8200,21 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
@@ -8318,18 +8348,21 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
@@ -8463,12 +8496,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8608,12 +8641,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -8622,9 +8655,12 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8750,12 +8786,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -8764,9 +8800,12 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -8892,12 +8931,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -8906,9 +8945,12 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9034,12 +9076,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9048,9 +9090,12 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9176,12 +9221,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9190,9 +9235,12 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9318,12 +9366,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9332,9 +9380,12 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9460,12 +9511,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9474,9 +9525,12 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9602,12 +9656,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -9616,9 +9670,12 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9714,12 +9771,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9744,18 +9801,21 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
@@ -9792,40 +9852,7012 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW64" t="inlineStr">
+      <c r="AW69" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
+      <c r="AX69" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr">
+      <c r="AY69" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
+      <c r="AZ69" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA64" t="inlineStr">
+      <c r="BA69" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB64" t="inlineStr">
+      <c r="BB69" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC64" t="inlineStr">
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -9947,7 +16979,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -9957,7 +16989,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d093/2026-2029.xlsx
+++ b/diseases/d093/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2084,6 +2129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2232,6 +2282,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2380,6 +2435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2528,6 +2588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2676,6 +2741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2824,6 +2894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2969,6 +3044,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3114,6 +3194,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3259,6 +3344,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3404,6 +3494,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3549,6 +3644,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3694,6 +3794,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3839,6 +3944,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3984,6 +4094,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4132,6 +4247,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4280,6 +4400,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4428,6 +4553,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4576,6 +4706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4724,6 +4859,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4869,6 +5009,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5014,6 +5159,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5159,6 +5309,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5304,6 +5459,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5449,6 +5609,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5594,6 +5759,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5739,6 +5909,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5884,6 +6059,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6032,6 +6212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6180,6 +6365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6328,6 +6518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6476,6 +6671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6621,6 +6821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6766,6 +6971,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6911,6 +7121,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7056,6 +7271,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7201,6 +7421,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7346,6 +7571,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7491,6 +7721,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7636,6 +7871,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7781,6 +8021,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7929,6 +8174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8077,6 +8327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8225,6 +8480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8373,6 +8633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8518,6 +8783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8663,6 +8933,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8808,6 +9083,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8953,6 +9233,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9098,6 +9383,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9243,6 +9533,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9388,6 +9683,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9533,6 +9833,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9678,6 +9983,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9826,6 +10136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9974,6 +10289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10122,6 +10442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10270,6 +10595,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10418,6 +10748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10563,6 +10898,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10708,6 +11048,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10853,6 +11198,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10998,6 +11348,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11143,6 +11498,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11288,6 +11648,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11433,6 +11798,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11578,6 +11948,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11723,6 +12098,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11868,6 +12248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12013,6 +12398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12158,6 +12548,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12303,6 +12698,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12448,6 +12848,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12593,6 +12998,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12738,6 +13148,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12883,6 +13298,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13028,6 +13448,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13173,6 +13598,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13318,6 +13748,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13463,6 +13898,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13608,6 +14048,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13753,6 +14198,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13898,6 +14348,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14043,6 +14498,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14188,6 +14648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14333,6 +14798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14478,6 +14948,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14623,6 +15098,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14768,6 +15248,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14913,6 +15398,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15058,6 +15548,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15203,6 +15698,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15348,6 +15848,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15493,6 +15998,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15638,6 +16148,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15783,6 +16298,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15928,6 +16448,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16073,6 +16598,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16218,6 +16748,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16363,6 +16898,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16508,6 +17048,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16653,6 +17198,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16796,6 +17346,11 @@
       <c r="S112" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">

--- a/diseases/d093/2026-2029.xlsx
+++ b/diseases/d093/2026-2029.xlsx
@@ -2271,9 +2271,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -2424,9 +2421,6 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -6201,9 +6195,6 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -6507,9 +6498,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -10430,9 +10418,6 @@
       </c>
       <c r="O66" t="n">
         <v>1</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0.0002865038132769385</v>

--- a/diseases/d093/2026-2029.xlsx
+++ b/diseases/d093/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1071,11 +1041,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1088,22 +1053,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1221,11 +1176,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1238,22 +1188,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1371,11 +1311,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1388,22 +1323,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1521,11 +1446,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1538,22 +1458,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1671,11 +1581,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1688,22 +1593,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1821,11 +1716,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1838,22 +1728,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1971,11 +1851,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1988,22 +1863,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2883,11 +2748,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2900,22 +2760,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3033,11 +2883,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3050,22 +2895,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3183,11 +3018,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3200,22 +3030,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3333,11 +3153,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3350,22 +3165,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3483,11 +3288,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3500,22 +3300,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3633,11 +3423,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3650,22 +3435,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3783,11 +3558,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3800,22 +3570,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3933,11 +3693,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3950,22 +3705,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4083,11 +3828,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4100,22 +3840,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4848,11 +4578,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4865,22 +4590,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4998,11 +4713,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5015,22 +4725,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5148,11 +4848,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5165,22 +4860,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5298,11 +4983,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5315,22 +4995,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5448,11 +5118,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5465,22 +5130,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5598,11 +5253,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5615,22 +5265,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5748,11 +5388,6 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5765,22 +5400,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5898,11 +5523,6 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5915,22 +5535,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6048,11 +5658,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6065,22 +5670,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6804,11 +6399,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6821,22 +6411,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6954,11 +6534,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6971,22 +6546,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7104,11 +6669,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7121,22 +6681,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7254,11 +6804,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7271,22 +6816,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7404,11 +6939,6 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7421,22 +6951,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7554,11 +7074,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7571,22 +7086,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7704,11 +7209,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7721,22 +7221,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7854,11 +7344,6 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7871,22 +7356,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8004,11 +7479,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8021,22 +7491,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8766,11 +8226,6 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8783,22 +8238,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8916,11 +8361,6 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8933,22 +8373,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9066,11 +8496,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9083,22 +8508,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9216,11 +8631,6 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9233,22 +8643,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9366,11 +8766,6 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9383,22 +8778,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9516,11 +8901,6 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9533,22 +8913,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9666,11 +9036,6 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9683,22 +9048,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9816,11 +9171,6 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9833,22 +9183,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9966,11 +9306,6 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9983,22 +9318,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10878,11 +10203,6 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10895,22 +10215,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11028,11 +10338,6 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11045,22 +10350,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11178,11 +10473,6 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11195,22 +10485,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11328,11 +10608,6 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11345,22 +10620,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11478,11 +10743,6 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11495,22 +10755,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11628,11 +10878,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11645,22 +10890,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11778,11 +11013,6 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11795,22 +11025,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11928,11 +11148,6 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11945,22 +11160,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12078,11 +11283,6 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12095,22 +11295,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12828,11 +12018,6 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12845,22 +12030,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12978,11 +12153,6 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12995,22 +12165,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13128,11 +12288,6 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13145,22 +12300,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13278,11 +12423,6 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13295,22 +12435,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13428,11 +12558,6 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13445,22 +12570,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13578,11 +12693,6 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13595,22 +12705,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13728,11 +12828,6 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13745,22 +12840,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13878,11 +12963,6 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13895,22 +12975,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14028,11 +13098,6 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14045,22 +13110,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14778,11 +13833,6 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14795,22 +13845,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14928,11 +13968,6 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14945,22 +13980,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15078,11 +14103,6 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15095,22 +14115,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15228,11 +14238,6 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15245,22 +14250,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15378,11 +14373,6 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15395,22 +14385,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15528,11 +14508,6 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15545,22 +14520,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15678,11 +14643,6 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15695,22 +14655,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15828,11 +14778,6 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15845,22 +14790,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15978,11 +14913,6 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15995,22 +14925,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16128,11 +15048,6 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16145,22 +15060,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16278,11 +15183,6 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16295,22 +15195,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16428,11 +15318,6 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16445,22 +15330,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16578,11 +15453,6 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16595,22 +15465,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16728,11 +15588,6 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16745,22 +15600,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16878,11 +15723,6 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16895,22 +15735,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17028,11 +15858,6 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17045,22 +15870,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17178,11 +15993,6 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17195,22 +16005,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17328,11 +16128,6 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17345,22 +16140,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>

--- a/diseases/d093/2026-2029.xlsx
+++ b/diseases/d093/2026-2029.xlsx
@@ -1983,17 +1983,15 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2006,22 +2004,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2136,14 +2124,12 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2156,22 +2142,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2286,14 +2262,12 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2306,22 +2280,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2436,17 +2400,15 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2459,22 +2421,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2589,17 +2541,15 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2612,22 +2562,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3960,17 +3900,15 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3983,22 +3921,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4113,17 +4041,15 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4136,22 +4062,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4266,17 +4182,15 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4289,22 +4203,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4419,17 +4323,15 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4442,22 +4344,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5790,14 +5682,12 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
       <c r="R38" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5810,22 +5700,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5940,17 +5820,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5963,22 +5841,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6093,14 +5961,12 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
       <c r="R40" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6113,22 +5979,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6243,17 +6099,15 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6266,22 +6120,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7611,17 +7455,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7634,22 +7476,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7764,17 +7596,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7787,22 +7617,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7917,17 +7737,15 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7940,22 +7758,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8070,17 +7878,15 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8093,22 +7899,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9438,17 +9234,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9461,22 +9255,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9591,17 +9375,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9614,22 +9396,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9744,14 +9516,12 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
       <c r="R66" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9764,22 +9534,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9894,17 +9654,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9917,22 +9675,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10047,17 +9795,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10070,22 +9816,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11415,14 +11151,12 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11435,22 +11169,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11565,14 +11289,12 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11585,22 +11307,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11715,14 +11427,12 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11735,22 +11445,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11865,14 +11565,12 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11885,22 +11583,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13230,14 +12918,12 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13250,22 +12936,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13380,14 +13056,12 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13400,22 +13074,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13530,14 +13194,12 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13550,22 +13212,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13680,14 +13332,12 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13700,22 +13350,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>

--- a/diseases/d093/2026-2029.xlsx
+++ b/diseases/d093/2026-2029.xlsx
@@ -15828,6 +15828,141 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>chancroid</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D093</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Chancroid</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>软下疳</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15861,7 +15996,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -15944,7 +16079,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -15954,7 +16089,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d093/2026-2029.xlsx
+++ b/diseases/d093/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +938,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1041,6 +1071,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1053,12 +1088,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1176,6 +1221,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1188,12 +1238,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1311,6 +1371,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1323,12 +1388,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1446,6 +1521,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1458,12 +1538,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1581,6 +1671,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1593,12 +1688,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1716,6 +1821,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1728,12 +1838,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1851,6 +1971,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1863,12 +1988,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2688,6 +2823,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2700,12 +2840,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2823,6 +2973,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2835,12 +2990,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2958,6 +3123,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2970,12 +3140,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3093,6 +3273,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3105,12 +3290,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3228,6 +3423,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3240,12 +3440,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3363,6 +3573,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3375,12 +3590,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3498,6 +3723,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3510,12 +3740,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3633,6 +3873,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3645,12 +3890,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3768,6 +4023,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3780,12 +4040,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4470,6 +4740,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4482,12 +4757,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4605,6 +4890,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4617,12 +4907,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4740,6 +5040,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4752,12 +5057,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4875,6 +5190,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4887,12 +5207,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5010,6 +5340,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5022,12 +5357,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5145,6 +5490,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5157,12 +5507,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5280,6 +5640,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5292,12 +5657,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5415,6 +5790,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5427,12 +5807,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5550,6 +5940,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5562,12 +5957,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6243,6 +6648,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6255,12 +6665,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6378,6 +6798,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6390,12 +6815,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6513,6 +6948,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6525,12 +6965,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6648,6 +7098,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6660,12 +7115,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6783,6 +7248,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6795,12 +7265,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -6918,6 +7398,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6930,12 +7415,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7053,6 +7548,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7065,12 +7565,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7188,6 +7698,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7200,12 +7715,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7323,6 +7848,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7335,12 +7865,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8022,6 +8562,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8034,12 +8579,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8157,6 +8712,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8169,12 +8729,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8292,6 +8862,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8304,12 +8879,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8427,6 +9012,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8439,12 +9029,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8562,6 +9162,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8574,12 +9179,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8697,6 +9312,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8709,12 +9329,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8832,6 +9462,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8844,12 +9479,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -8967,6 +9612,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8979,12 +9629,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9102,6 +9762,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9114,12 +9779,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9939,6 +10614,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9951,12 +10631,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10074,6 +10764,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10086,12 +10781,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10209,6 +10914,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10221,12 +10931,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10344,6 +11064,11 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10356,12 +11081,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10479,6 +11214,11 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10491,12 +11231,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -10614,6 +11364,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10626,12 +11381,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -10749,6 +11514,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10761,12 +11531,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -10884,6 +11664,11 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10896,12 +11681,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11019,6 +11814,11 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11031,12 +11831,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11706,6 +12516,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11718,12 +12533,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -11841,6 +12666,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11853,12 +12683,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -11976,6 +12816,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11988,12 +12833,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12111,6 +12966,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12123,12 +12983,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12246,6 +13116,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12258,12 +13133,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12381,6 +13266,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12393,12 +13283,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12516,6 +13416,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12528,12 +13433,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -12651,6 +13566,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12663,12 +13583,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -12786,6 +13716,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12798,12 +13733,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13473,6 +14418,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13485,12 +14435,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -13608,6 +14568,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13620,12 +14585,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -13743,6 +14718,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13755,12 +14735,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -13878,6 +14868,11 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13890,12 +14885,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14013,6 +15018,11 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14025,12 +15035,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14148,6 +15168,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14160,12 +15185,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14283,6 +15318,11 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14295,12 +15335,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14418,6 +15468,11 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14430,12 +15485,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -14553,6 +15618,11 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14565,12 +15635,22 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -14688,6 +15768,11 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14700,12 +15785,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -14823,6 +15918,11 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14835,12 +15935,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -14958,6 +16068,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14970,12 +16085,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15093,6 +16218,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15105,12 +16235,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15228,6 +16368,11 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15240,12 +16385,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -15363,6 +16518,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15375,12 +16535,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -15498,6 +16668,11 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15510,12 +16685,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -15633,6 +16818,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15645,12 +16835,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -15768,6 +16968,11 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15780,12 +16985,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -15903,6 +17118,11 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15915,12 +17135,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
